--- a/backend/data/financials_by_company/08N.WA.xlsx
+++ b/backend/data/financials_by_company/08N.WA.xlsx
@@ -662,55 +662,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-293719.460129</v>
+        <v>-9425</v>
       </c>
       <c r="C2" t="n">
-        <v>0.039526</v>
+        <v>0.1625</v>
       </c>
       <c r="D2" t="n">
-        <v>-6124000</v>
+        <v>-5872000</v>
       </c>
       <c r="E2" t="n">
-        <v>-7431000</v>
+        <v>-58000</v>
       </c>
       <c r="F2" t="n">
-        <v>-7431000</v>
+        <v>-58000</v>
       </c>
       <c r="G2" t="n">
-        <v>-13739000</v>
+        <v>-3698000</v>
       </c>
       <c r="H2" t="n">
-        <v>1000</v>
+        <v>192000</v>
       </c>
       <c r="I2" t="n">
-        <v>-13555000</v>
+        <v>-5930000</v>
       </c>
       <c r="J2" t="n">
-        <v>-13556000</v>
+        <v>-6122000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1619000</v>
+        <v>-468000</v>
       </c>
       <c r="L2" t="n">
-        <v>966000</v>
+        <v>358000</v>
       </c>
       <c r="M2" t="n">
-        <v>99000</v>
+        <v>102000</v>
       </c>
       <c r="N2" t="n">
-        <v>-6601719.460129</v>
+        <v>-3649425</v>
       </c>
       <c r="O2" t="n">
-        <v>-13739000</v>
+        <v>-3698000</v>
       </c>
       <c r="P2" t="n">
-        <v>4173000</v>
+        <v>2203000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-12728000</v>
+        <v>-5439000</v>
       </c>
       <c r="R2" t="n">
         <v>42786848</v>
@@ -719,144 +719,140 @@
         <v>42786848</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.32</v>
+        <v>-0.09</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.32</v>
+        <v>-0.09</v>
       </c>
       <c r="V2" t="n">
-        <v>-13739000</v>
+        <v>-3698000</v>
       </c>
       <c r="W2" t="n">
-        <v>-13739000</v>
+        <v>-3698000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-13739000</v>
+        <v>-3698000</v>
       </c>
       <c r="Z2" t="n">
-        <v>209000</v>
+        <v>1729000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-13948000</v>
+        <v>-5427000</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-13948000</v>
+        <v>-5427000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-574000</v>
+        <v>-1053000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-14522000</v>
+        <v>-6480000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-7351000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>804000</v>
-      </c>
+        <v>-188000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>6547000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
+        <v>188000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>-1619000</v>
+        <v>-468000</v>
       </c>
       <c r="AK2" t="n">
-        <v>752000</v>
+        <v>212000</v>
       </c>
       <c r="AL2" t="n">
-        <v>966000</v>
+        <v>358000</v>
       </c>
       <c r="AM2" t="n">
-        <v>99000</v>
+        <v>102000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-2971000</v>
+        <v>-1313000</v>
       </c>
       <c r="AO2" t="n">
-        <v>4173000</v>
+        <v>2203000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1198000</v>
+        <v>11000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1000</v>
+        <v>192000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1000</v>
+        <v>192000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2348000</v>
+        <v>1341000</v>
       </c>
       <c r="AT2" t="n">
-        <v>2348000</v>
+        <v>1341000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1202000</v>
+        <v>890000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1202000</v>
+        <v>890000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-304574.733096</v>
+        <v>-256500</v>
       </c>
       <c r="C3" t="n">
-        <v>0.177491</v>
+        <v>0.19</v>
       </c>
       <c r="D3" t="n">
-        <v>7412000</v>
+        <v>-1162000</v>
       </c>
       <c r="E3" t="n">
-        <v>-1716000</v>
+        <v>-1350000</v>
       </c>
       <c r="F3" t="n">
-        <v>-1716000</v>
+        <v>-1350000</v>
       </c>
       <c r="G3" t="n">
-        <v>3724000</v>
+        <v>-4705000</v>
       </c>
       <c r="H3" t="n">
-        <v>331000</v>
+        <v>392000</v>
       </c>
       <c r="I3" t="n">
-        <v>5696000</v>
+        <v>-2512000</v>
       </c>
       <c r="J3" t="n">
-        <v>5365000</v>
+        <v>-2904000</v>
       </c>
       <c r="K3" t="n">
-        <v>-614000</v>
+        <v>-512000</v>
       </c>
       <c r="L3" t="n">
-        <v>869000</v>
+        <v>671000</v>
       </c>
       <c r="M3" t="n">
-        <v>255000</v>
+        <v>159000</v>
       </c>
       <c r="N3" t="n">
-        <v>5135425.266904</v>
+        <v>-3611500</v>
       </c>
       <c r="O3" t="n">
-        <v>3724000</v>
+        <v>-4704000</v>
       </c>
       <c r="P3" t="n">
-        <v>2801000</v>
+        <v>2941000</v>
       </c>
       <c r="Q3" t="n">
-        <v>4800000</v>
+        <v>-2684000</v>
       </c>
       <c r="R3" t="n">
         <v>42786848</v>
@@ -865,140 +861,138 @@
         <v>42786848</v>
       </c>
       <c r="T3" t="n">
-        <v>0.09</v>
+        <v>-0.09</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09</v>
+        <v>-0.09</v>
       </c>
       <c r="V3" t="n">
-        <v>3724000</v>
+        <v>-4704000</v>
       </c>
       <c r="W3" t="n">
-        <v>3724000</v>
+        <v>-4704000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>3724000</v>
+        <v>-4704000</v>
       </c>
       <c r="Z3" t="n">
-        <v>26000</v>
+        <v>-163000</v>
       </c>
       <c r="AA3" t="n">
-        <v>3698000</v>
+        <v>-4541000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>3698000</v>
+        <v>-4542000</v>
       </c>
       <c r="AD3" t="n">
-        <v>798000</v>
+        <v>967000</v>
       </c>
       <c r="AE3" t="n">
-        <v>4496000</v>
+        <v>-3575000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-36000</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>36000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
+        <v>5000</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>-614000</v>
+        <v>-512000</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>869000</v>
+        <v>671000</v>
       </c>
       <c r="AM3" t="n">
-        <v>255000</v>
+        <v>159000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1592000</v>
+        <v>-1817000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2801000</v>
+        <v>2941000</v>
       </c>
       <c r="AP3" t="n">
-        <v>36000</v>
+        <v>126000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>331000</v>
+        <v>392000</v>
       </c>
       <c r="AR3" t="n">
-        <v>331000</v>
+        <v>392000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1850000</v>
+        <v>1842000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1850000</v>
+        <v>1842000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1209000</v>
+        <v>1124000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1209000</v>
+        <v>1124000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-256500</v>
+        <v>-304574.733096</v>
       </c>
       <c r="C4" t="n">
-        <v>0.19</v>
+        <v>0.177491</v>
       </c>
       <c r="D4" t="n">
-        <v>-1162000</v>
+        <v>7412000</v>
       </c>
       <c r="E4" t="n">
-        <v>-1350000</v>
+        <v>-1716000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1350000</v>
+        <v>-1716000</v>
       </c>
       <c r="G4" t="n">
-        <v>-4705000</v>
+        <v>3724000</v>
       </c>
       <c r="H4" t="n">
-        <v>392000</v>
+        <v>331000</v>
       </c>
       <c r="I4" t="n">
-        <v>-2512000</v>
+        <v>5696000</v>
       </c>
       <c r="J4" t="n">
-        <v>-2904000</v>
+        <v>5365000</v>
       </c>
       <c r="K4" t="n">
-        <v>-512000</v>
+        <v>-614000</v>
       </c>
       <c r="L4" t="n">
-        <v>671000</v>
+        <v>869000</v>
       </c>
       <c r="M4" t="n">
-        <v>159000</v>
+        <v>255000</v>
       </c>
       <c r="N4" t="n">
-        <v>-3611500</v>
+        <v>5135425.266904</v>
       </c>
       <c r="O4" t="n">
-        <v>-4704000</v>
+        <v>3724000</v>
       </c>
       <c r="P4" t="n">
-        <v>2941000</v>
+        <v>2801000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2684000</v>
+        <v>4800000</v>
       </c>
       <c r="R4" t="n">
         <v>42786848</v>
@@ -1007,138 +1001,140 @@
         <v>42786848</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.09</v>
+        <v>0.09</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.09</v>
+        <v>0.09</v>
       </c>
       <c r="V4" t="n">
-        <v>-4704000</v>
+        <v>3724000</v>
       </c>
       <c r="W4" t="n">
-        <v>-4704000</v>
+        <v>3724000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-4704000</v>
+        <v>3724000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-163000</v>
+        <v>26000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-4541000</v>
+        <v>3698000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4542000</v>
+        <v>3698000</v>
       </c>
       <c r="AD4" t="n">
-        <v>967000</v>
+        <v>798000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-3575000</v>
+        <v>4496000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>-36000</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>36000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>-512000</v>
+        <v>-614000</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>671000</v>
+        <v>869000</v>
       </c>
       <c r="AM4" t="n">
-        <v>159000</v>
+        <v>255000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1817000</v>
+        <v>-1592000</v>
       </c>
       <c r="AO4" t="n">
-        <v>2941000</v>
+        <v>2801000</v>
       </c>
       <c r="AP4" t="n">
-        <v>126000</v>
+        <v>36000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>392000</v>
+        <v>331000</v>
       </c>
       <c r="AR4" t="n">
-        <v>392000</v>
+        <v>331000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1842000</v>
+        <v>1850000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1842000</v>
+        <v>1850000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1124000</v>
+        <v>1209000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1124000</v>
+        <v>1209000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-9425</v>
+        <v>-293719.460129</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1625</v>
+        <v>0.039526</v>
       </c>
       <c r="D5" t="n">
-        <v>-5872000</v>
+        <v>-6124000</v>
       </c>
       <c r="E5" t="n">
-        <v>-58000</v>
+        <v>-7431000</v>
       </c>
       <c r="F5" t="n">
-        <v>-58000</v>
+        <v>-7431000</v>
       </c>
       <c r="G5" t="n">
-        <v>-3698000</v>
+        <v>-13739000</v>
       </c>
       <c r="H5" t="n">
-        <v>192000</v>
+        <v>1000</v>
       </c>
       <c r="I5" t="n">
-        <v>-5930000</v>
+        <v>-13555000</v>
       </c>
       <c r="J5" t="n">
-        <v>-6122000</v>
+        <v>-13556000</v>
       </c>
       <c r="K5" t="n">
-        <v>-468000</v>
+        <v>-1619000</v>
       </c>
       <c r="L5" t="n">
-        <v>358000</v>
+        <v>966000</v>
       </c>
       <c r="M5" t="n">
-        <v>102000</v>
+        <v>99000</v>
       </c>
       <c r="N5" t="n">
-        <v>-3649425</v>
+        <v>-6601719.460129</v>
       </c>
       <c r="O5" t="n">
-        <v>-3698000</v>
+        <v>-13739000</v>
       </c>
       <c r="P5" t="n">
-        <v>2203000</v>
+        <v>4173000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5439000</v>
+        <v>-12728000</v>
       </c>
       <c r="R5" t="n">
         <v>42786848</v>
@@ -1147,87 +1143,91 @@
         <v>42786848</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.09</v>
+        <v>-0.32</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.09</v>
+        <v>-0.32</v>
       </c>
       <c r="V5" t="n">
-        <v>-3698000</v>
+        <v>-13739000</v>
       </c>
       <c r="W5" t="n">
-        <v>-3698000</v>
+        <v>-13739000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-3698000</v>
+        <v>-13739000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1729000</v>
+        <v>209000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-5427000</v>
+        <v>-13948000</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-5427000</v>
+        <v>-13948000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1053000</v>
+        <v>-574000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-6480000</v>
+        <v>-14522000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-188000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>-7351000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>804000</v>
+      </c>
       <c r="AH5" t="n">
-        <v>188000</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>6547000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>-468000</v>
+        <v>-1619000</v>
       </c>
       <c r="AK5" t="n">
-        <v>212000</v>
+        <v>752000</v>
       </c>
       <c r="AL5" t="n">
-        <v>358000</v>
+        <v>966000</v>
       </c>
       <c r="AM5" t="n">
-        <v>102000</v>
+        <v>99000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1313000</v>
+        <v>-2971000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2203000</v>
+        <v>4173000</v>
       </c>
       <c r="AP5" t="n">
-        <v>11000</v>
+        <v>1198000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>192000</v>
+        <v>1000</v>
       </c>
       <c r="AR5" t="n">
-        <v>192000</v>
+        <v>1000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1341000</v>
+        <v>2348000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1341000</v>
+        <v>2348000</v>
       </c>
       <c r="AU5" t="n">
-        <v>890000</v>
+        <v>1202000</v>
       </c>
       <c r="AV5" t="n">
-        <v>890000</v>
+        <v>1202000</v>
       </c>
     </row>
   </sheetData>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>42786848</v>
@@ -1562,46 +1562,46 @@
         <v>42786848</v>
       </c>
       <c r="D2" t="n">
-        <v>20262000</v>
+        <v>12021000</v>
       </c>
       <c r="E2" t="n">
-        <v>23828000</v>
+        <v>20720000</v>
       </c>
       <c r="F2" t="n">
-        <v>42028000</v>
+        <v>56186000</v>
       </c>
       <c r="G2" t="n">
-        <v>63378000</v>
+        <v>74424000</v>
       </c>
       <c r="H2" t="n">
-        <v>7314000</v>
+        <v>18609000</v>
       </c>
       <c r="I2" t="n">
-        <v>42028000</v>
+        <v>56186000</v>
       </c>
       <c r="J2" t="n">
-        <v>2478000</v>
+        <v>2494000</v>
       </c>
       <c r="K2" t="n">
-        <v>42028000</v>
+        <v>56198000</v>
       </c>
       <c r="L2" t="n">
-        <v>49459000</v>
+        <v>64378000</v>
       </c>
       <c r="M2" t="n">
-        <v>42705000</v>
+        <v>56966000</v>
       </c>
       <c r="N2" t="n">
-        <v>677000</v>
+        <v>768000</v>
       </c>
       <c r="O2" t="n">
-        <v>42028000</v>
+        <v>56198000</v>
       </c>
       <c r="P2" t="n">
-        <v>26302000</v>
+        <v>27626000</v>
       </c>
       <c r="Q2" t="n">
-        <v>11382000</v>
+        <v>24228000</v>
       </c>
       <c r="R2" t="n">
         <v>4279000</v>
@@ -1610,128 +1610,134 @@
         <v>4279000</v>
       </c>
       <c r="T2" t="n">
-        <v>26559000</v>
+        <v>23014000</v>
       </c>
       <c r="U2" t="n">
-        <v>12236000</v>
+        <v>12567000</v>
       </c>
       <c r="V2" t="n">
-        <v>296000</v>
+        <v>307000</v>
       </c>
       <c r="W2" t="n">
-        <v>242000</v>
+        <v>381000</v>
       </c>
       <c r="X2" t="n">
-        <v>1795000</v>
+        <v>1210000</v>
       </c>
       <c r="Y2" t="n">
-        <v>9903000</v>
+        <v>10669000</v>
       </c>
       <c r="Z2" t="n">
-        <v>2472000</v>
+        <v>2489000</v>
       </c>
       <c r="AA2" t="n">
-        <v>7431000</v>
+        <v>8180000</v>
       </c>
       <c r="AB2" t="n">
-        <v>14323000</v>
+        <v>10447000</v>
       </c>
       <c r="AC2" t="n">
-        <v>13925000</v>
+        <v>10051000</v>
       </c>
       <c r="AD2" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="AE2" t="n">
-        <v>13919000</v>
+        <v>10046000</v>
       </c>
       <c r="AF2" t="n">
-        <v>149000</v>
+        <v>212000</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="AI2" t="n">
-        <v>143000</v>
+        <v>207000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>69264000</v>
+        <v>79980000</v>
       </c>
       <c r="AK2" t="n">
-        <v>47627000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>50924000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
       <c r="AM2" t="n">
-        <v>12555000</v>
+        <v>18056000</v>
       </c>
       <c r="AN2" t="n">
-        <v>12555000</v>
+        <v>18056000</v>
       </c>
       <c r="AO2" t="n">
-        <v>34989000</v>
+        <v>15761000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>15117000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-220000</v>
+        <v>-525000</v>
       </c>
       <c r="AU2" t="n">
+        <v>15642000</v>
+      </c>
+      <c r="AV2" t="n">
         <v>220000</v>
       </c>
-      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
         <v>220000</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>14855000</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>567000</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>21637000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>542000</v>
-      </c>
+        <v>29056000</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>45000</v>
+        <v>19000</v>
       </c>
       <c r="BD2" t="n">
-        <v>121000</v>
+        <v>68000</v>
       </c>
       <c r="BE2" t="n">
-        <v>19735000</v>
+        <v>1608000</v>
       </c>
       <c r="BF2" t="n">
-        <v>1194000</v>
+        <v>27361000</v>
       </c>
       <c r="BG2" t="n">
-        <v>106000</v>
+        <v>21156000</v>
       </c>
       <c r="BH2" t="n">
-        <v>1088000</v>
+        <v>6205000</v>
       </c>
       <c r="BI2" t="n">
-        <v>209000</v>
+        <v>4163000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>879000</v>
+        <v>2042000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>42786848</v>
@@ -1740,46 +1746,46 @@
         <v>42786848</v>
       </c>
       <c r="D3" t="n">
-        <v>16892000</v>
+        <v>13167000</v>
       </c>
       <c r="E3" t="n">
-        <v>21183000</v>
+        <v>20851000</v>
       </c>
       <c r="F3" t="n">
-        <v>55766000</v>
+        <v>51976000</v>
       </c>
       <c r="G3" t="n">
-        <v>74467000</v>
+        <v>70358000</v>
       </c>
       <c r="H3" t="n">
-        <v>18779000</v>
+        <v>17373000</v>
       </c>
       <c r="I3" t="n">
-        <v>55766000</v>
+        <v>51976000</v>
       </c>
       <c r="J3" t="n">
-        <v>2483000</v>
+        <v>2488000</v>
       </c>
       <c r="K3" t="n">
-        <v>55767000</v>
+        <v>51995000</v>
       </c>
       <c r="L3" t="n">
-        <v>63827000</v>
+        <v>59839000</v>
       </c>
       <c r="M3" t="n">
-        <v>56653000</v>
+        <v>52907000</v>
       </c>
       <c r="N3" t="n">
-        <v>886000</v>
+        <v>912000</v>
       </c>
       <c r="O3" t="n">
-        <v>55767000</v>
+        <v>51995000</v>
       </c>
       <c r="P3" t="n">
-        <v>37842000</v>
+        <v>25538000</v>
       </c>
       <c r="Q3" t="n">
-        <v>13581000</v>
+        <v>22113000</v>
       </c>
       <c r="R3" t="n">
         <v>4279000</v>
@@ -1788,130 +1794,134 @@
         <v>4279000</v>
       </c>
       <c r="T3" t="n">
-        <v>24661000</v>
+        <v>24218000</v>
       </c>
       <c r="U3" t="n">
-        <v>13641000</v>
+        <v>13090000</v>
       </c>
       <c r="V3" t="n">
-        <v>278000</v>
+        <v>280000</v>
       </c>
       <c r="W3" t="n">
-        <v>334000</v>
+        <v>718000</v>
       </c>
       <c r="X3" t="n">
-        <v>2491000</v>
+        <v>1765000</v>
       </c>
       <c r="Y3" t="n">
-        <v>10538000</v>
+        <v>10327000</v>
       </c>
       <c r="Z3" t="n">
-        <v>2478000</v>
+        <v>2483000</v>
       </c>
       <c r="AA3" t="n">
-        <v>8060000</v>
+        <v>7844000</v>
       </c>
       <c r="AB3" t="n">
-        <v>11020000</v>
+        <v>11128000</v>
       </c>
       <c r="AC3" t="n">
-        <v>10645000</v>
+        <v>10524000</v>
       </c>
       <c r="AD3" t="n">
         <v>5000</v>
       </c>
       <c r="AE3" t="n">
-        <v>10640000</v>
+        <v>10519000</v>
       </c>
       <c r="AF3" t="n">
-        <v>126000</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>329000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3000</v>
+      </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>109000</v>
       </c>
       <c r="AI3" t="n">
-        <v>125000</v>
+        <v>217000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>81314000</v>
+        <v>77125000</v>
       </c>
       <c r="AK3" t="n">
-        <v>51515000</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+        <v>48624000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
       <c r="AM3" t="n">
-        <v>12727000</v>
+        <v>14791000</v>
       </c>
       <c r="AN3" t="n">
-        <v>12727000</v>
+        <v>14791000</v>
       </c>
       <c r="AO3" t="n">
-        <v>38689000</v>
+        <v>15863000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1000</v>
+        <v>19000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1000</v>
+        <v>19000</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>14676000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1231000</v>
+        <v>-917000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1231000</v>
+        <v>15593000</v>
       </c>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
         <v>220000</v>
       </c>
       <c r="AX3" t="n">
-        <v>1011000</v>
+        <v>14806000</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>567000</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>29799000</v>
+        <v>28501000</v>
       </c>
       <c r="BB3" t="n">
-        <v>477000</v>
+        <v>479000</v>
       </c>
       <c r="BC3" t="n">
-        <v>32000</v>
+        <v>20000</v>
       </c>
       <c r="BD3" t="n">
-        <v>114000</v>
+        <v>102000</v>
       </c>
       <c r="BE3" t="n">
-        <v>1516000</v>
+        <v>1548000</v>
       </c>
       <c r="BF3" t="n">
-        <v>27660000</v>
+        <v>26352000</v>
       </c>
       <c r="BG3" t="n">
-        <v>25852000</v>
+        <v>21156000</v>
       </c>
       <c r="BH3" t="n">
-        <v>1808000</v>
+        <v>5196000</v>
       </c>
       <c r="BI3" t="n">
-        <v>841000</v>
+        <v>1473000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>967000</v>
+        <v>3723000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>42786848</v>
@@ -1920,46 +1930,46 @@
         <v>42786848</v>
       </c>
       <c r="D4" t="n">
-        <v>13167000</v>
+        <v>16892000</v>
       </c>
       <c r="E4" t="n">
-        <v>20851000</v>
+        <v>21183000</v>
       </c>
       <c r="F4" t="n">
-        <v>51976000</v>
+        <v>55766000</v>
       </c>
       <c r="G4" t="n">
-        <v>70358000</v>
+        <v>74467000</v>
       </c>
       <c r="H4" t="n">
-        <v>17373000</v>
+        <v>18779000</v>
       </c>
       <c r="I4" t="n">
-        <v>51976000</v>
+        <v>55766000</v>
       </c>
       <c r="J4" t="n">
-        <v>2488000</v>
+        <v>2483000</v>
       </c>
       <c r="K4" t="n">
-        <v>51995000</v>
+        <v>55767000</v>
       </c>
       <c r="L4" t="n">
-        <v>59839000</v>
+        <v>63827000</v>
       </c>
       <c r="M4" t="n">
-        <v>52907000</v>
+        <v>56653000</v>
       </c>
       <c r="N4" t="n">
-        <v>912000</v>
+        <v>886000</v>
       </c>
       <c r="O4" t="n">
-        <v>51995000</v>
+        <v>55767000</v>
       </c>
       <c r="P4" t="n">
-        <v>25538000</v>
+        <v>37842000</v>
       </c>
       <c r="Q4" t="n">
-        <v>22113000</v>
+        <v>13581000</v>
       </c>
       <c r="R4" t="n">
         <v>4279000</v>
@@ -1968,134 +1978,130 @@
         <v>4279000</v>
       </c>
       <c r="T4" t="n">
-        <v>24218000</v>
+        <v>24661000</v>
       </c>
       <c r="U4" t="n">
-        <v>13090000</v>
+        <v>13641000</v>
       </c>
       <c r="V4" t="n">
-        <v>280000</v>
+        <v>278000</v>
       </c>
       <c r="W4" t="n">
-        <v>718000</v>
+        <v>334000</v>
       </c>
       <c r="X4" t="n">
-        <v>1765000</v>
+        <v>2491000</v>
       </c>
       <c r="Y4" t="n">
-        <v>10327000</v>
+        <v>10538000</v>
       </c>
       <c r="Z4" t="n">
-        <v>2483000</v>
+        <v>2478000</v>
       </c>
       <c r="AA4" t="n">
-        <v>7844000</v>
+        <v>8060000</v>
       </c>
       <c r="AB4" t="n">
-        <v>11128000</v>
+        <v>11020000</v>
       </c>
       <c r="AC4" t="n">
-        <v>10524000</v>
+        <v>10645000</v>
       </c>
       <c r="AD4" t="n">
         <v>5000</v>
       </c>
       <c r="AE4" t="n">
-        <v>10519000</v>
+        <v>10640000</v>
       </c>
       <c r="AF4" t="n">
-        <v>329000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3000</v>
-      </c>
+        <v>126000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>109000</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>217000</v>
+        <v>125000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>77125000</v>
+        <v>81314000</v>
       </c>
       <c r="AK4" t="n">
-        <v>48624000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
+        <v>51515000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>14791000</v>
+        <v>12727000</v>
       </c>
       <c r="AN4" t="n">
-        <v>14791000</v>
+        <v>12727000</v>
       </c>
       <c r="AO4" t="n">
-        <v>15863000</v>
+        <v>38689000</v>
       </c>
       <c r="AP4" t="n">
-        <v>19000</v>
+        <v>1000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19000</v>
+        <v>1000</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>14676000</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-917000</v>
+        <v>-1231000</v>
       </c>
       <c r="AU4" t="n">
-        <v>15593000</v>
+        <v>1231000</v>
       </c>
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
         <v>220000</v>
       </c>
       <c r="AX4" t="n">
-        <v>14806000</v>
+        <v>1011000</v>
       </c>
       <c r="AY4" t="n">
-        <v>567000</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>28501000</v>
+        <v>29799000</v>
       </c>
       <c r="BB4" t="n">
-        <v>479000</v>
+        <v>477000</v>
       </c>
       <c r="BC4" t="n">
-        <v>20000</v>
+        <v>32000</v>
       </c>
       <c r="BD4" t="n">
-        <v>102000</v>
+        <v>114000</v>
       </c>
       <c r="BE4" t="n">
-        <v>1548000</v>
+        <v>1516000</v>
       </c>
       <c r="BF4" t="n">
-        <v>26352000</v>
+        <v>27660000</v>
       </c>
       <c r="BG4" t="n">
-        <v>21156000</v>
+        <v>25852000</v>
       </c>
       <c r="BH4" t="n">
-        <v>5196000</v>
+        <v>1808000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1473000</v>
+        <v>841000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3723000</v>
+        <v>967000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>42786848</v>
@@ -2104,46 +2110,46 @@
         <v>42786848</v>
       </c>
       <c r="D5" t="n">
-        <v>12021000</v>
+        <v>20262000</v>
       </c>
       <c r="E5" t="n">
-        <v>20720000</v>
+        <v>23828000</v>
       </c>
       <c r="F5" t="n">
-        <v>56186000</v>
+        <v>42028000</v>
       </c>
       <c r="G5" t="n">
-        <v>74424000</v>
+        <v>63378000</v>
       </c>
       <c r="H5" t="n">
-        <v>18609000</v>
+        <v>7314000</v>
       </c>
       <c r="I5" t="n">
-        <v>56186000</v>
+        <v>42028000</v>
       </c>
       <c r="J5" t="n">
-        <v>2494000</v>
+        <v>2478000</v>
       </c>
       <c r="K5" t="n">
-        <v>56198000</v>
+        <v>42028000</v>
       </c>
       <c r="L5" t="n">
-        <v>64378000</v>
+        <v>49459000</v>
       </c>
       <c r="M5" t="n">
-        <v>56966000</v>
+        <v>42705000</v>
       </c>
       <c r="N5" t="n">
-        <v>768000</v>
+        <v>677000</v>
       </c>
       <c r="O5" t="n">
-        <v>56198000</v>
+        <v>42028000</v>
       </c>
       <c r="P5" t="n">
-        <v>27626000</v>
+        <v>26302000</v>
       </c>
       <c r="Q5" t="n">
-        <v>24228000</v>
+        <v>11382000</v>
       </c>
       <c r="R5" t="n">
         <v>4279000</v>
@@ -2152,129 +2158,123 @@
         <v>4279000</v>
       </c>
       <c r="T5" t="n">
-        <v>23014000</v>
+        <v>26559000</v>
       </c>
       <c r="U5" t="n">
-        <v>12567000</v>
+        <v>12236000</v>
       </c>
       <c r="V5" t="n">
-        <v>307000</v>
+        <v>296000</v>
       </c>
       <c r="W5" t="n">
-        <v>381000</v>
+        <v>242000</v>
       </c>
       <c r="X5" t="n">
-        <v>1210000</v>
+        <v>1795000</v>
       </c>
       <c r="Y5" t="n">
-        <v>10669000</v>
+        <v>9903000</v>
       </c>
       <c r="Z5" t="n">
-        <v>2489000</v>
+        <v>2472000</v>
       </c>
       <c r="AA5" t="n">
-        <v>8180000</v>
+        <v>7431000</v>
       </c>
       <c r="AB5" t="n">
-        <v>10447000</v>
+        <v>14323000</v>
       </c>
       <c r="AC5" t="n">
-        <v>10051000</v>
+        <v>13925000</v>
       </c>
       <c r="AD5" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="AE5" t="n">
-        <v>10046000</v>
+        <v>13919000</v>
       </c>
       <c r="AF5" t="n">
-        <v>212000</v>
+        <v>149000</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="AI5" t="n">
-        <v>207000</v>
+        <v>143000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>79980000</v>
+        <v>69264000</v>
       </c>
       <c r="AK5" t="n">
-        <v>50924000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
+        <v>47627000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>18056000</v>
+        <v>12555000</v>
       </c>
       <c r="AN5" t="n">
-        <v>18056000</v>
+        <v>12555000</v>
       </c>
       <c r="AO5" t="n">
-        <v>15761000</v>
+        <v>34989000</v>
       </c>
       <c r="AP5" t="n">
-        <v>12000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>15117000</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-525000</v>
+        <v>-220000</v>
       </c>
       <c r="AU5" t="n">
-        <v>15642000</v>
-      </c>
-      <c r="AV5" t="n">
         <v>220000</v>
       </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
         <v>220000</v>
       </c>
       <c r="AX5" t="n">
-        <v>14855000</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>567000</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>29056000</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
+        <v>21637000</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>542000</v>
+      </c>
       <c r="BC5" t="n">
-        <v>19000</v>
+        <v>45000</v>
       </c>
       <c r="BD5" t="n">
-        <v>68000</v>
+        <v>121000</v>
       </c>
       <c r="BE5" t="n">
-        <v>1608000</v>
+        <v>19735000</v>
       </c>
       <c r="BF5" t="n">
-        <v>27361000</v>
+        <v>1194000</v>
       </c>
       <c r="BG5" t="n">
-        <v>21156000</v>
+        <v>106000</v>
       </c>
       <c r="BH5" t="n">
-        <v>6205000</v>
+        <v>1088000</v>
       </c>
       <c r="BI5" t="n">
-        <v>4163000</v>
+        <v>209000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>2042000</v>
+        <v>879000</v>
       </c>
     </row>
   </sheetData>
@@ -2420,318 +2420,318 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-3688000</v>
+        <v>520000</v>
       </c>
       <c r="C2" t="n">
-        <v>-665000</v>
+        <v>-988000</v>
       </c>
       <c r="D2" t="n">
-        <v>2725000</v>
+        <v>1388000</v>
       </c>
       <c r="E2" t="n">
-        <v>1630000</v>
+        <v>6205000</v>
       </c>
       <c r="F2" t="n">
-        <v>2285000</v>
+        <v>7953000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-655000</v>
+        <v>-1748000</v>
       </c>
       <c r="I2" t="n">
-        <v>1363000</v>
+        <v>-63000</v>
       </c>
       <c r="J2" t="n">
-        <v>31000</v>
+        <v>-7000</v>
       </c>
       <c r="K2" t="n">
-        <v>-602000</v>
+        <v>-330000</v>
       </c>
       <c r="L2" t="n">
-        <v>2060000</v>
+        <v>400000</v>
       </c>
       <c r="M2" t="n">
-        <v>2060000</v>
+        <v>400000</v>
       </c>
       <c r="N2" t="n">
-        <v>-665000</v>
+        <v>-988000</v>
       </c>
       <c r="O2" t="n">
-        <v>2725000</v>
+        <v>1388000</v>
       </c>
       <c r="P2" t="n">
-        <v>1670000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>-2205000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-1000000</v>
+      </c>
       <c r="R2" t="n">
-        <v>1670000</v>
+        <v>-1205000</v>
       </c>
       <c r="S2" t="n">
-        <v>1670000</v>
+        <v>1277000</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-2482000</v>
       </c>
       <c r="U2" t="n">
-        <v>-3688000</v>
+        <v>520000</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>-13000</v>
       </c>
       <c r="W2" t="n">
-        <v>-3707000</v>
+        <v>-157000</v>
       </c>
       <c r="X2" t="n">
-        <v>-3707000</v>
+        <v>-157000</v>
       </c>
       <c r="Y2" t="n">
-        <v>19000</v>
+        <v>690000</v>
       </c>
       <c r="Z2" t="n">
-        <v>19000</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-3316000</v>
+        <v>-380000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1647000</v>
+        <v>-1327000</v>
       </c>
       <c r="D3" t="n">
-        <v>581000</v>
+        <v>391000</v>
       </c>
       <c r="E3" t="n">
-        <v>2285000</v>
+        <v>5675000</v>
       </c>
       <c r="F3" t="n">
-        <v>5675000</v>
+        <v>6205000</v>
       </c>
       <c r="G3" t="n">
-        <v>-50000</v>
+        <v>3000</v>
       </c>
       <c r="H3" t="n">
-        <v>-3340000</v>
+        <v>-533000</v>
       </c>
       <c r="I3" t="n">
-        <v>-1716000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>109000</v>
-      </c>
+        <v>-1535000</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>-633000</v>
+        <v>-473000</v>
       </c>
       <c r="L3" t="n">
-        <v>-1066000</v>
+        <v>-936000</v>
       </c>
       <c r="M3" t="n">
-        <v>-1066000</v>
+        <v>-936000</v>
       </c>
       <c r="N3" t="n">
-        <v>-1647000</v>
+        <v>-1327000</v>
       </c>
       <c r="O3" t="n">
-        <v>581000</v>
+        <v>391000</v>
       </c>
       <c r="P3" t="n">
-        <v>1692000</v>
+        <v>1382000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1692000</v>
+        <v>1440000</v>
       </c>
       <c r="R3" t="n">
-        <v>1692000</v>
+        <v>1382000</v>
       </c>
       <c r="S3" t="n">
-        <v>1692000</v>
+        <v>1440000</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-58000</v>
       </c>
       <c r="U3" t="n">
-        <v>-3316000</v>
+        <v>-380000</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-3338000</v>
+        <v>-2678000</v>
       </c>
       <c r="X3" t="n">
-        <v>-3338000</v>
+        <v>-2678000</v>
       </c>
       <c r="Y3" t="n">
-        <v>22000</v>
+        <v>2298000</v>
       </c>
       <c r="Z3" t="n">
-        <v>22000</v>
+        <v>2298000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-380000</v>
+        <v>-3316000</v>
       </c>
       <c r="C4" t="n">
-        <v>-1327000</v>
+        <v>-1647000</v>
       </c>
       <c r="D4" t="n">
-        <v>391000</v>
+        <v>581000</v>
       </c>
       <c r="E4" t="n">
+        <v>2285000</v>
+      </c>
+      <c r="F4" t="n">
         <v>5675000</v>
       </c>
-      <c r="F4" t="n">
-        <v>6205000</v>
-      </c>
       <c r="G4" t="n">
-        <v>3000</v>
+        <v>-50000</v>
       </c>
       <c r="H4" t="n">
-        <v>-533000</v>
+        <v>-3340000</v>
       </c>
       <c r="I4" t="n">
-        <v>-1535000</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>-1716000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>109000</v>
+      </c>
       <c r="K4" t="n">
-        <v>-473000</v>
+        <v>-633000</v>
       </c>
       <c r="L4" t="n">
-        <v>-936000</v>
+        <v>-1066000</v>
       </c>
       <c r="M4" t="n">
-        <v>-936000</v>
+        <v>-1066000</v>
       </c>
       <c r="N4" t="n">
-        <v>-1327000</v>
+        <v>-1647000</v>
       </c>
       <c r="O4" t="n">
-        <v>391000</v>
+        <v>581000</v>
       </c>
       <c r="P4" t="n">
-        <v>1382000</v>
+        <v>1692000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1440000</v>
+        <v>1692000</v>
       </c>
       <c r="R4" t="n">
-        <v>1382000</v>
+        <v>1692000</v>
       </c>
       <c r="S4" t="n">
-        <v>1440000</v>
+        <v>1692000</v>
       </c>
       <c r="T4" t="n">
-        <v>-58000</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-380000</v>
+        <v>-3316000</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-2678000</v>
+        <v>-3338000</v>
       </c>
       <c r="X4" t="n">
-        <v>-2678000</v>
+        <v>-3338000</v>
       </c>
       <c r="Y4" t="n">
-        <v>2298000</v>
+        <v>22000</v>
       </c>
       <c r="Z4" t="n">
-        <v>2298000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>520000</v>
+        <v>-3688000</v>
       </c>
       <c r="C5" t="n">
-        <v>-988000</v>
+        <v>-665000</v>
       </c>
       <c r="D5" t="n">
-        <v>1388000</v>
+        <v>2725000</v>
       </c>
       <c r="E5" t="n">
-        <v>6205000</v>
+        <v>1630000</v>
       </c>
       <c r="F5" t="n">
-        <v>7953000</v>
+        <v>2285000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-1748000</v>
+        <v>-655000</v>
       </c>
       <c r="I5" t="n">
-        <v>-63000</v>
+        <v>1363000</v>
       </c>
       <c r="J5" t="n">
-        <v>-7000</v>
+        <v>31000</v>
       </c>
       <c r="K5" t="n">
-        <v>-330000</v>
+        <v>-602000</v>
       </c>
       <c r="L5" t="n">
-        <v>400000</v>
+        <v>2060000</v>
       </c>
       <c r="M5" t="n">
-        <v>400000</v>
+        <v>2060000</v>
       </c>
       <c r="N5" t="n">
-        <v>-988000</v>
+        <v>-665000</v>
       </c>
       <c r="O5" t="n">
-        <v>1388000</v>
+        <v>2725000</v>
       </c>
       <c r="P5" t="n">
-        <v>-2205000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-1000000</v>
-      </c>
+        <v>1670000</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>-1205000</v>
+        <v>1670000</v>
       </c>
       <c r="S5" t="n">
-        <v>1277000</v>
+        <v>1670000</v>
       </c>
       <c r="T5" t="n">
-        <v>-2482000</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>520000</v>
+        <v>-3688000</v>
       </c>
       <c r="V5" t="n">
-        <v>-13000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-157000</v>
+        <v>-3707000</v>
       </c>
       <c r="X5" t="n">
-        <v>-157000</v>
+        <v>-3707000</v>
       </c>
       <c r="Y5" t="n">
-        <v>690000</v>
+        <v>19000</v>
       </c>
       <c r="Z5" t="n">
-        <v>690000</v>
+        <v>19000</v>
       </c>
     </row>
   </sheetData>
@@ -3231,167 +3231,167 @@
       </c>
       <c r="CS1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="DZ1" t="inlineStr">
@@ -3494,55 +3494,55 @@
         <v>0.625</v>
       </c>
       <c r="U2" t="n">
-        <v>0.665</v>
+        <v>0.625</v>
       </c>
       <c r="V2" t="n">
-        <v>0.665</v>
+        <v>0.625</v>
       </c>
       <c r="W2" t="n">
-        <v>0.665</v>
+        <v>0.625</v>
       </c>
       <c r="X2" t="n">
         <v>0.625</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.665</v>
+        <v>0.625</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.665</v>
+        <v>0.625</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.665</v>
+        <v>0.625</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.171</v>
+        <v>0.135</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>808</v>
+        <v>818</v>
       </c>
       <c r="AG2" t="n">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="AH2" t="n">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.67</v>
       </c>
       <c r="AK2" t="n">
-        <v>28453254</v>
+        <v>26741780</v>
       </c>
       <c r="AL2" t="n">
         <v>26741780</v>
@@ -3551,7 +3551,7 @@
         <v>0.61</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.845</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AO2" t="n">
         <v>3.95</v>
@@ -3560,13 +3560,13 @@
         <v>0.55</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-11.80633</v>
+        <v>-11.096174</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.646</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.688825</v>
+        <v>0.68165</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>36917500</v>
+        <v>34465780</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -3601,10 +3601,10 @@
         <v>42786848</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.956</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.71351933</v>
+        <v>0.65376574</v>
       </c>
       <c r="BF2" t="n">
         <v>1735603200</v>
@@ -3622,16 +3622,16 @@
         <v>-0.12</v>
       </c>
       <c r="BK2" t="n">
-        <v>-15.318</v>
+        <v>-14.301</v>
       </c>
       <c r="BL2" t="n">
-        <v>-6.827</v>
+        <v>-6.374</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.23780489</v>
+        <v>-0.22839504</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="BP2" t="n">
-        <v>0.665</v>
+        <v>0.625</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         <v>12111000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.276</v>
+        <v>0.283</v>
       </c>
       <c r="BT2" t="n">
         <v>-5407667</v>
@@ -3745,124 +3745,124 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CT2" t="n">
+        <v>1782120591</v>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>08OCTAVA</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>NFI Octava S.A.</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
           <t>WSE</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>finmb_3483664</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>Europe/Warsaw</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>CEST</t>
         </is>
       </c>
-      <c r="CW2" t="n">
+      <c r="DA2" t="n">
         <v>7200000</v>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>pl_market</t>
         </is>
       </c>
-      <c r="CY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CZ2" t="n">
+      <c r="DC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Warsaw</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>818</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.014999986</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.02459014</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>0.61 - 0.81</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.185</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.22839506</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-22.839504</v>
+      </c>
+      <c r="DN2" t="n">
         <v>-0.12</v>
       </c>
-      <c r="DA2" t="n">
-        <v>0.013300002</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>0.020408165</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>-0.02382499</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>-0.03458787</v>
-      </c>
-      <c r="DE2" t="n">
+      <c r="DO2" t="n">
+        <v>-0.021000028</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.03250778</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.056649983</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.08310714</v>
+      </c>
+      <c r="DS2" t="n">
         <v>15</v>
       </c>
-      <c r="DF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>1780390799</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>08OCTAVA</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>NFI Octava S.A.</t>
-        </is>
-      </c>
-      <c r="DL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
+      <c r="DT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
         <v>1266825600000</v>
       </c>
-      <c r="DN2" t="n">
-        <v>0.04000002</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>0.665 - 0.665</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>Warsaw</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>808</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.055000007</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.09016394599999999</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>0.61 - 0.845</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.21301775</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-23.780489</v>
-      </c>
       <c r="DX2" t="n">
-        <v>6.4000034</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.665</v>
+        <v>0</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>0.625 - 0.625</t>
+        </is>
       </c>
       <c r="DZ2" t="inlineStr"/>
     </row>
